--- a/pdf2img/tabel/table_9.xlsx
+++ b/pdf2img/tabel/table_9.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K89"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,12 +489,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>berakhir</t>
+          <t>yang</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>pada</t>
+          <t>berakhir,pada</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -504,15 +504,19 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Desember,;2025</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>dan’2024</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Desember,2025</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>dan'2024</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -520,13 +524,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>{</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>dalam</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>jutaan</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>rupiah</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>)</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -537,11 +557,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+          <t>POS-POS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>31-Des-25</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>31-Des-24</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -554,27 +582,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>(</t>
+          <t>ARUS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>dalam</t>
+          <t>KAS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>jutaan</t>
+          <t>DARI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>rupiah</t>
+          <t>AKTIVITAS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>)</t>
+          <t>OPERASI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -587,21 +615,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>POS-POS</t>
+          <t>Penerimaan</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>31-Des-25</t>
+          <t>bunga</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>31-Des-24</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+          <t>dan</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>komisi</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>9.290.357</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -612,29 +648,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARUS</t>
+          <t>Pembayaran</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KAS</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>DARI</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>AKTIVITAS</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>OPERASI</t>
-        </is>
-      </c>
+          <t>bunga</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -645,29 +669,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Penerimaan</t>
+          <t>Pendapatan</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bunga</t>
+          <t>operasional</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dan</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>komisi</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>9.290.357</t>
-        </is>
-      </c>
+          <t>lainnya</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -683,11 +699,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bunga</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>beban</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>operasional</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>lainnya</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
@@ -699,17 +723,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pendapatan</t>
+          <t>Penerimaan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>operasional</t>
+          <t>pendapatan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lainnya</t>
+          <t>non-operasional</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -734,14 +758,10 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>operasional</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>lainnya</t>
-        </is>
-      </c>
+          <t>non-operasional</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -753,20 +773,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Penerimaan</t>
+          <t>Pembayaran</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>pendapatan</t>
+          <t>beban</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>non-operasional</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>pajak</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>penghasilan</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -778,52 +802,88 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pembayaran</t>
+          <t>Arus</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>beban</t>
+          <t>kas</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>non-operasional</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+          <t>sebelum</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>perubahan</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>dalam</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>aset</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>dan</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>liabilitas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>operasi</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pembayaran</t>
+          <t>Perubahan</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>beban</t>
+          <t>dalam</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>pajak</t>
+          <t>aset</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>penghasilan</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+          <t>dan</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>liabilitas</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>operasi</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
@@ -832,84 +892,68 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Arus</t>
+          <t>Penurunan/(kenaikan)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>kas</t>
+          <t>aset</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>sebelum</t>
+          <t>operasi</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>perubahan</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>dalam</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>aset</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>dan</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>liabilitas</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>operasi</t>
-        </is>
-      </c>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Perubahan</t>
+          <t>Penempatan</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>dalam</t>
+          <t>pada</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>aset</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>dan</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>liabilitas</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>operasi</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>lain</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
@@ -918,15 +962,39 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+          <t>Efek-efek</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>yang</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>dibeli</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>dengan</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>janji</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>dijual</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>kembali</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
@@ -935,17 +1003,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Penurunan/(kenaikan)</t>
+          <t>Pinjaman</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>aset</t>
+          <t>yang</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>operasi</t>
+          <t>diberikan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -960,11 +1028,19 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
+          <t>Biaya</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>dibayar</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>dimuka</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
@@ -977,39 +1053,19 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Penempatan</t>
+          <t>Aset</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>pada</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>dan</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>bank</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>lain</t>
-        </is>
-      </c>
+          <t>Lain-lain</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
@@ -1018,34 +1074,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Efek-efek</t>
+          <t>Kenaikan/(penurunan)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>dibeli</t>
+          <t>liabilitas</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dengan</t>
+          <t>operasi</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>janji</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>dijual</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>kembali</t>
-        </is>
-      </c>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1055,11 +1103,19 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
+          <t>Simpanan</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>nasabah</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
@@ -1072,14 +1128,10 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pinjaman</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>diberikan</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
@@ -1093,10 +1145,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t>Giro</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>921.831</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
@@ -1110,19 +1166,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Biaya</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>dibayar</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>dimuka</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
@@ -1135,12 +1183,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aset</t>
+          <t>Tabungan</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lain-lain</t>
+          <t>815.138</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -1156,20 +1204,24 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kenaikan/(penurunan)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>liabilitas</t>
+          <t>Deposito</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>operasi</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Berjangka</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>10.666.433</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
@@ -1181,12 +1233,24 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+          <t>Simpanan</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>dari</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>lain</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
@@ -1198,12 +1262,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Simpanan</t>
+          <t>Utang</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nasabah</t>
+          <t>pajak</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -1219,15 +1283,39 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+          <t>Efek-efek</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>yang</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>dijual</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>dengan</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>janji</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>dibeli</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>kembali</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
@@ -1236,12 +1324,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Giro</t>
+          <t>Liabilitas</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>921.831</t>
+          <t>[ain-lain</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -1257,15 +1345,39 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+          <t>Kas</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>neto</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>yang</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>diperoleh</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>dari</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>aktivitas</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>operasi</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
@@ -1274,17 +1386,29 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Tabungan</t>
+          <t>ARUS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>815.138</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+          <t>KAS</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>DARI</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AKTIVITAS</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>INVESTASI</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
@@ -1295,12 +1419,24 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+          <t>Hasil</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>penjualan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>aset</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>tetap</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
@@ -1312,24 +1448,44 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Deposito</t>
+          <t>Pembelian</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Berjangka</t>
+          <t>aset</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>10.666.433</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+          <t>tetap</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>dan</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>aset</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>yang</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>belum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>digunakan</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -1337,15 +1493,39 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+          <t>Pembelian</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>efek-efek</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>yang</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>wajar</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>diukur</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>melalui</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
@@ -1354,24 +1534,20 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Simpanan</t>
+          <t>penghasilan</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>dari</t>
+          <t>komprehensif</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>bank</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
           <t>lain</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
@@ -1383,19 +1559,39 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Utang</t>
+          <t>Penerimaan</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>pajak</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+          <t>dari</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>efek-efek</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>yang</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>telah</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>jatuh</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>tempo</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
@@ -1404,51 +1600,83 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Efek-efek</t>
+          <t>yang</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>dijual</t>
+          <t>nilai</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>dengan</t>
+          <t>wajar</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>janji</t>
+          <t>diukur</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>dibeli</t>
+          <t>melalui</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>kembali</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+          <t>penghasilan</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>komprehensif</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>lain</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>726.745</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Pembelian</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>efek-efek</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>yang</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>diukur</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>pada</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>biaya</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -1458,15 +1686,19 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Liabilitas</t>
+          <t>perolehan</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>lain-lain</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>diamortisasi</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>(1.539.311)</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
@@ -1479,37 +1711,49 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Kas</t>
+          <t>Penerimaan</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>neto</t>
+          <t>dari</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>diperoleh</t>
+          <t>efek-efek</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>dari</t>
+          <t>yang</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>aktivitas</t>
+          <t>diukur</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>operasi</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+          <t>pada</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>biaya</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>perolehan</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>diamortisasi</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
     </row>
@@ -1519,10 +1763,26 @@
           <t>yang</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>telah</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>jatuh</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>tempo</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2.891.000</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
@@ -1533,31 +1793,39 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ARUS</t>
+          <t>Kas</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>KAS</t>
+          <t>neto</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DARI</t>
+          <t>yang</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>AKTIVITAS</t>
+          <t>diperoleh</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>INVESTASI</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+          <t>dari</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>aktivitas</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>investasi</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
@@ -1566,25 +1834,29 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Hasil</t>
+          <t>ARUS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>penjualan</t>
+          <t>KAS</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>aset</t>
+          <t>DARI</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>tetap</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
+          <t>AKTIVITAS</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>PENDANAAN</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
@@ -1595,39 +1867,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Pembelian</t>
+          <t>Pembayaran</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>aset</t>
+          <t>obligasi</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>tetap</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>dan</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>aset</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>belum</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>digunakan</t>
-        </is>
-      </c>
+          <t>subordinasi</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
@@ -1636,13 +1892,29 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+          <t>Penerimaan</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>uang</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>muka</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>setoran</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>modal</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
@@ -1653,34 +1925,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Pembelian</t>
+          <t>Pembayaran</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>efek-efek</t>
+          <t>liabilitas</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>nilai</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>wajar</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>diukur</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>melalui</t>
-        </is>
-      </c>
+          <t>sewa</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -1690,13 +1950,29 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>Penerimaan</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>(pembayaran)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>pinjaman</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
           <t>yang</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>diterima</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
@@ -1707,59 +1983,87 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>penghasilan</t>
+          <t>Kas</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>komprehensif</t>
+          <t>neto</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>lain</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+          <t>yang</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>diperoleh</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>dari</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>(digunakan</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>untuk)</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>aktivitas</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>pendanaan</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>880.304</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>(853.698</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Penerimaan</t>
+          <t>Kenaikan</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>dari</t>
+          <t>kas</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>efek-efek</t>
+          <t>dan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>telah</t>
+          <t>setara</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>jatuh</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>tempo</t>
-        </is>
-      </c>
+          <t>kas</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -1769,77 +2073,137 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+          <t>Kas</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>dan</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>setara</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>kas</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>pada</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>awal</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tahun</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>17.968.285</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>17.840.731</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>nilai</t>
+          <t>Kas</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>wajar</t>
+          <t>dan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>diukur</t>
+          <t>setara</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>melalui</t>
+          <t>kas</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>penghasilan</t>
+          <t>pada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>komprehensif</t>
+          <t>akhir</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>lain</t>
+          <t>periode</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>726.745</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>23.405.323</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>17.968.285</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
+          <t>Kas</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>dan</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Setara</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Kas</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>terdiri</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>dari</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
@@ -1848,29 +2212,21 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Pembelian</t>
+          <t>Kas</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>efek-efek</t>
+          <t>365.577</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>diukur</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>pada</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>biaya</t>
-        </is>
-      </c>
+          <t>374.523</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
@@ -1881,14 +2237,34 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
+          <t>Giro</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>pada</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>8.625.761</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>8.933.209</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
@@ -1898,22 +2274,34 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>perolehan</t>
+          <t>Giro</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>diamortisasi</t>
+          <t>pada</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>(1.539.311)</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>lain</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1.619.800</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>531.791</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -1923,52 +2311,56 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Penerimaan</t>
+          <t>Penempatan</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>dari</t>
+          <t>pada</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>efek-efek</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>diukur</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>pada</t>
+          <t>dan</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>biaya</t>
+          <t>bank</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>perolehan</t>
+          <t>lain</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>diamortisasi</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>jangka</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>wakiu</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>yang</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -1985,69 +2377,101 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>yang</t>
+          <t>jatuh</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>telah</t>
+          <t>tempo</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>jatuh</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>tempo</t>
+          <t>bulan</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2.891.000</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+          <t>atau</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>kurang</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>sejak</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>tanggal</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>perolehan</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>11.426.915</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>6.327.800</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Kas</t>
+          <t>Efek-efek</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>neto</t>
+          <t>jangka</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>diperoleh</t>
+          <t>waktu</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>dari</t>
+          <t>jatuh</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>aktivitas</t>
+          <t>tempo</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>investasi</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>bulan</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>atau</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
@@ -2055,7 +2479,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>yang</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2072,30 +2496,34 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ARUS</t>
+          <t>kurang</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>KAS</t>
+          <t>sejak</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DARI</t>
+          <t>tanggal</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>AKTIVITAS</t>
+          <t>perolehan</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>PENDANAAN</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
+          <t>1.367.270</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1.800.962</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -2105,784 +2533,44 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Pembayaran</t>
+          <t>JUMLAH</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>obligasi</t>
+          <t>KAS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>subordinasi</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
+          <t>DAN</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>SETARA</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>KAS</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>23.405.323</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>17.968.285</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Penerimaan</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>muka</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>setoran</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>medal</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>uang</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Pembayaran</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>liabilitas</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>sewa</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Penerimaan</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>(pembayaran)</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>pinjaman</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>diterima</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Kas</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>neto</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>diperoleh</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>dari</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>(digunakan</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>untuk)</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>aktivitas</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>pendanaan</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>880.304</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>(853.698</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Kenaikan</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>kas</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>dan</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>setara</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>kas</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Kas</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>dan</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>setara</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>kas</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>pada</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>awal</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Tahun</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>17.968.285</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>17.840.731</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Kas</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>dan</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>kas</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>pada</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>akhir</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>periode</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>23.405.323</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>17.968.285</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>setara</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Kas</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>dan</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Setara</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Kas</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>terdiri</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>dari:</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Kas</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>365.577</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>374,523</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Giro</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>pada</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>8.625.761</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>8.933.209</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Giro</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>pada</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>bank</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>lain</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>1.619.800</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>531.791</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Penempatan</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>pada</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>dan</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>bank</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>lain</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>jangka</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>waktu</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>jatuh</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>tempo</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>bulan</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>atau</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Kurang</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>sejak</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>tanggal</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>perolehan</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>11.426.915</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>6.327.800</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Efek-efek</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>jangka</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>waktu</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>jatuh</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>bulan</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>tempo</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>atau</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>kurang</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>sejak</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>tanggal</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>perolehan</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>1.367.270</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>1.800.962</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>JUMLAH</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>KAS</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>DAN</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>SETARA</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>KAS</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>23.405.323</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>17.968.285</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
